--- a/artfynd/A 64870-2023 artfynd.xlsx
+++ b/artfynd/A 64870-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64870-2023 artfynd.xlsx
+++ b/artfynd/A 64870-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113337134</v>
+        <v>113337125</v>
       </c>
       <c r="B2" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,8 +703,16 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581841</v>
+        <v>581916</v>
       </c>
       <c r="R2" t="n">
-        <v>6320897</v>
+        <v>6320899</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,54 +785,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113337021</v>
+        <v>113337134</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -838,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581847</v>
+        <v>581841</v>
       </c>
       <c r="R3" t="n">
-        <v>6320893</v>
+        <v>6320897</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,12 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,55 +887,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113337047</v>
+        <v>113406449</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581880</v>
+        <v>581755</v>
       </c>
       <c r="R4" t="n">
-        <v>6320876</v>
+        <v>6320576</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,12 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +982,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,55 +1000,46 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113337035</v>
+        <v>113406808</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1076,13 +1047,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581881</v>
+        <v>581417</v>
       </c>
       <c r="R5" t="n">
-        <v>6320893</v>
+        <v>6320565</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,12 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1091,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1139,55 +1109,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113336998</v>
+        <v>116472836</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1195,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581806</v>
+        <v>581656</v>
       </c>
       <c r="R6" t="n">
-        <v>6320747</v>
+        <v>6320697</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,12 +1186,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1200,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,66 +1218,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113336990</v>
+        <v>116453688</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Granshult 1:7, Sm</t>
+          <t>Bräkamossen, Bräkamossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581786</v>
+        <v>581426</v>
       </c>
       <c r="R7" t="n">
-        <v>6320742</v>
+        <v>6320691</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,12 +1288,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-19</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,34 +1302,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113337140</v>
+        <v>113336990</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,7 +1350,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1433,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581820</v>
+        <v>581786</v>
       </c>
       <c r="R8" t="n">
-        <v>6320884</v>
+        <v>6320742</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1496,15 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113406428</v>
+        <v>113336998</v>
       </c>
       <c r="B9" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1464,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1552,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581741</v>
+        <v>581806</v>
       </c>
       <c r="R9" t="n">
-        <v>6320583</v>
+        <v>6320747</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1582,12 +1515,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,15 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113406459</v>
+        <v>113337021</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1578,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1671,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581777</v>
+        <v>581847</v>
       </c>
       <c r="R10" t="n">
-        <v>6320589</v>
+        <v>6320893</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1701,12 +1629,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,15 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113406485</v>
+        <v>113337035</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,7 +1692,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1790,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581827</v>
+        <v>581881</v>
       </c>
       <c r="R11" t="n">
-        <v>6320563</v>
+        <v>6320893</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1820,12 +1743,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,15 +1776,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113406532</v>
+        <v>113337047</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,7 +1806,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1909,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581362</v>
+        <v>581880</v>
       </c>
       <c r="R12" t="n">
-        <v>6320744</v>
+        <v>6320876</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1939,12 +1857,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,15 +1890,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113406480</v>
+        <v>113337140</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +1920,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2028,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581779</v>
+        <v>581820</v>
       </c>
       <c r="R13" t="n">
-        <v>6320562</v>
+        <v>6320884</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2058,12 +1971,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2023-11-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,15 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113406627</v>
+        <v>113406355</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,7 +2034,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2147,10 +2055,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581305</v>
+        <v>581800</v>
       </c>
       <c r="R14" t="n">
-        <v>6320582</v>
+        <v>6320752</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2210,15 +2118,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113406690</v>
+        <v>113406360</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2148,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2266,10 +2169,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581424</v>
+        <v>581719</v>
       </c>
       <c r="R15" t="n">
-        <v>6320587</v>
+        <v>6320719</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2329,15 +2232,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113406384</v>
+        <v>113406366</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,7 +2262,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2385,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581742</v>
+        <v>581717</v>
       </c>
       <c r="R16" t="n">
-        <v>6320660</v>
+        <v>6320699</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2448,15 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113406360</v>
+        <v>113406384</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2483,7 +2376,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2504,10 +2397,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581719</v>
+        <v>581742</v>
       </c>
       <c r="R17" t="n">
-        <v>6320719</v>
+        <v>6320660</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2567,15 +2460,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113406509</v>
+        <v>113406391</v>
       </c>
       <c r="B18" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2602,7 +2490,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2623,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581381</v>
+        <v>581723</v>
       </c>
       <c r="R18" t="n">
-        <v>6320713</v>
+        <v>6320612</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2686,15 +2574,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113406391</v>
+        <v>113406428</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2604,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2742,10 +2625,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581723</v>
+        <v>581741</v>
       </c>
       <c r="R19" t="n">
-        <v>6320612</v>
+        <v>6320583</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2805,15 +2688,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>116473019</v>
+        <v>113406459</v>
       </c>
       <c r="B20" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2718,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2861,13 +2739,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581413</v>
+        <v>581777</v>
       </c>
       <c r="R20" t="n">
-        <v>6320610</v>
+        <v>6320589</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2891,12 +2769,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2924,42 +2802,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113406585</v>
+        <v>113406468</v>
       </c>
       <c r="B21" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2980,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581371</v>
+        <v>581765</v>
       </c>
       <c r="R21" t="n">
-        <v>6320640</v>
+        <v>6320562</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3043,15 +2916,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113406699</v>
+        <v>113406480</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +2946,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3099,10 +2967,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581390</v>
+        <v>581779</v>
       </c>
       <c r="R22" t="n">
-        <v>6320580</v>
+        <v>6320562</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3165,12 +3033,7 @@
         <v>113406484</v>
       </c>
       <c r="B23" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3281,15 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113406703</v>
+        <v>113406485</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3316,7 +3174,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3337,10 +3195,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581396</v>
+        <v>581827</v>
       </c>
       <c r="R24" t="n">
-        <v>6320584</v>
+        <v>6320563</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3400,15 +3258,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>113406355</v>
+        <v>113406492</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3435,7 +3288,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3456,10 +3309,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581800</v>
+        <v>581466</v>
       </c>
       <c r="R25" t="n">
-        <v>6320752</v>
+        <v>6320661</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3519,15 +3372,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113406611</v>
+        <v>113406498</v>
       </c>
       <c r="B26" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3554,7 +3402,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3575,10 +3423,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581291</v>
+        <v>581428</v>
       </c>
       <c r="R26" t="n">
-        <v>6320617</v>
+        <v>6320682</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3641,12 +3489,7 @@
         <v>113406501</v>
       </c>
       <c r="B27" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3757,15 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113406649</v>
+        <v>113406509</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3792,7 +3630,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3813,10 +3651,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581324</v>
+        <v>581381</v>
       </c>
       <c r="R28" t="n">
-        <v>6320559</v>
+        <v>6320713</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3876,15 +3714,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113406366</v>
+        <v>113406523</v>
       </c>
       <c r="B29" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3911,7 +3744,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3932,10 +3765,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581717</v>
+        <v>581366</v>
       </c>
       <c r="R29" t="n">
-        <v>6320699</v>
+        <v>6320707</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3995,15 +3828,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113406492</v>
+        <v>113406532</v>
       </c>
       <c r="B30" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4030,7 +3858,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4051,10 +3879,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581466</v>
+        <v>581362</v>
       </c>
       <c r="R30" t="n">
-        <v>6320661</v>
+        <v>6320744</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4114,15 +3942,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113406604</v>
+        <v>113406541</v>
       </c>
       <c r="B31" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4149,7 +3972,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4170,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581322</v>
+        <v>581342</v>
       </c>
       <c r="R31" t="n">
-        <v>6320613</v>
+        <v>6320739</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4233,15 +4056,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113406541</v>
+        <v>113406550</v>
       </c>
       <c r="B32" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4268,7 +4086,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4289,10 +4107,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581342</v>
+        <v>581315</v>
       </c>
       <c r="R32" t="n">
-        <v>6320739</v>
+        <v>6320715</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4352,51 +4170,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113406808</v>
+        <v>113406558</v>
       </c>
       <c r="B33" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4404,13 +4221,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581417</v>
+        <v>581324</v>
       </c>
       <c r="R33" t="n">
-        <v>6320565</v>
+        <v>6320682</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4448,6 +4265,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4466,42 +4284,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113406529</v>
+        <v>113406573</v>
       </c>
       <c r="B34" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4522,10 +4335,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581370</v>
+        <v>581335</v>
       </c>
       <c r="R34" t="n">
-        <v>6320727</v>
+        <v>6320648</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4588,12 +4401,7 @@
         <v>113406597</v>
       </c>
       <c r="B35" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4704,15 +4512,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113406523</v>
+        <v>113406604</v>
       </c>
       <c r="B36" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4739,7 +4542,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4760,10 +4563,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581366</v>
+        <v>581322</v>
       </c>
       <c r="R36" t="n">
-        <v>6320707</v>
+        <v>6320613</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4823,15 +4626,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113406738</v>
+        <v>113406611</v>
       </c>
       <c r="B37" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4858,7 +4656,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4879,10 +4677,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581355</v>
+        <v>581291</v>
       </c>
       <c r="R37" t="n">
-        <v>6320562</v>
+        <v>6320617</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4942,15 +4740,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113406673</v>
+        <v>113406627</v>
       </c>
       <c r="B38" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4977,7 +4770,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4998,10 +4791,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581391</v>
+        <v>581305</v>
       </c>
       <c r="R38" t="n">
-        <v>6320619</v>
+        <v>6320582</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5061,15 +4854,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113406763</v>
+        <v>113406649</v>
       </c>
       <c r="B39" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5096,7 +4884,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5117,10 +4905,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581388</v>
+        <v>581324</v>
       </c>
       <c r="R39" t="n">
-        <v>6320495</v>
+        <v>6320559</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5180,15 +4968,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113406749</v>
+        <v>113406669</v>
       </c>
       <c r="B40" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5215,7 +4998,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5236,10 +5019,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581359</v>
+        <v>581345</v>
       </c>
       <c r="R40" t="n">
-        <v>6320536</v>
+        <v>6320584</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5299,15 +5082,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>113406550</v>
+        <v>113406673</v>
       </c>
       <c r="B41" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5334,7 +5112,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5355,10 +5133,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581315</v>
+        <v>581391</v>
       </c>
       <c r="R41" t="n">
-        <v>6320715</v>
+        <v>6320619</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5418,15 +5196,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>113406669</v>
+        <v>116473019</v>
       </c>
       <c r="B42" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5453,7 +5226,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5474,13 +5247,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581345</v>
+        <v>581413</v>
       </c>
       <c r="R42" t="n">
-        <v>6320584</v>
+        <v>6320610</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5504,12 +5277,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5537,15 +5310,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113406558</v>
+        <v>113406690</v>
       </c>
       <c r="B43" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5572,7 +5340,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5593,10 +5361,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581324</v>
+        <v>581424</v>
       </c>
       <c r="R43" t="n">
-        <v>6320682</v>
+        <v>6320587</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5656,15 +5424,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113406468</v>
+        <v>113406699</v>
       </c>
       <c r="B44" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5691,7 +5454,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5712,10 +5475,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581765</v>
+        <v>581390</v>
       </c>
       <c r="R44" t="n">
-        <v>6320562</v>
+        <v>6320580</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5775,15 +5538,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113406716</v>
+        <v>113406703</v>
       </c>
       <c r="B45" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5810,7 +5568,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5831,10 +5589,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581360</v>
+        <v>581396</v>
       </c>
       <c r="R45" t="n">
-        <v>6320566</v>
+        <v>6320584</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5894,15 +5652,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>113406573</v>
+        <v>113406716</v>
       </c>
       <c r="B46" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5929,7 +5682,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5950,10 +5703,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581335</v>
+        <v>581360</v>
       </c>
       <c r="R46" t="n">
-        <v>6320648</v>
+        <v>6320566</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -6013,15 +5766,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113406498</v>
+        <v>113406738</v>
       </c>
       <c r="B47" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6048,7 +5796,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6069,10 +5817,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581428</v>
+        <v>581355</v>
       </c>
       <c r="R47" t="n">
-        <v>6320682</v>
+        <v>6320562</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -6132,55 +5880,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113406449</v>
+        <v>113406749</v>
       </c>
       <c r="B48" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6188,10 +5931,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581755</v>
+        <v>581359</v>
       </c>
       <c r="R48" t="n">
-        <v>6320576</v>
+        <v>6320536</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6232,6 +5975,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6250,15 +5994,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>116473035</v>
+        <v>113406763</v>
       </c>
       <c r="B49" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6285,7 +6024,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6306,13 +6045,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581344</v>
+        <v>581388</v>
       </c>
       <c r="R49" t="n">
-        <v>6320709</v>
+        <v>6320495</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6336,12 +6075,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6372,12 +6111,7 @@
         <v>116452742</v>
       </c>
       <c r="B50" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6414,7 +6148,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bräkamossen (Bräkamossen), Sm</t>
+          <t>Bräkamossen, Bräkamossen, Sm</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -6480,58 +6214,64 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>116453688</v>
+        <v>116473035</v>
       </c>
       <c r="B51" t="n">
-        <v>57426</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bräkamossen (Bräkamossen), Sm</t>
+          <t>Granshult 1:7, Sm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581426</v>
+        <v>581344</v>
       </c>
       <c r="R51" t="n">
-        <v>6320691</v>
+        <v>6320709</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6569,69 +6309,69 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>116472836</v>
+        <v>116473071</v>
       </c>
       <c r="B52" t="n">
-        <v>57293</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6639,13 +6379,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581656</v>
+        <v>581360</v>
       </c>
       <c r="R52" t="n">
-        <v>6320697</v>
+        <v>6320735</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6683,6 +6423,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6701,42 +6442,37 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>116473071</v>
+        <v>113406529</v>
       </c>
       <c r="B53" t="n">
-        <v>97767</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6757,13 +6493,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581360</v>
+        <v>581370</v>
       </c>
       <c r="R53" t="n">
-        <v>6320735</v>
+        <v>6320727</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6787,12 +6523,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6817,6 +6553,120 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>113406585</v>
+      </c>
+      <c r="B54" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Granshult 1:7, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>581371</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6320640</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-11-24</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64870-2023 artfynd.xlsx
+++ b/artfynd/A 64870-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337125</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337134</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406449</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406808</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116472836</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116453688</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113336990</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113336998</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337021</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1773,6 +1823,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337035</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337047</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,6 +2061,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113337140</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406355</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2229,6 +2299,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406360</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2343,6 +2418,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406366</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2457,6 +2537,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406384</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2571,6 +2656,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406391</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2685,6 +2775,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406428</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2799,6 +2894,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406459</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2913,6 +3013,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406468</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3027,6 +3132,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406480</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3141,6 +3251,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406484</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3255,6 +3370,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406485</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3369,6 +3489,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406492</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3483,6 +3608,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406498</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3597,6 +3727,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406501</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3711,6 +3846,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406509</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3825,6 +3965,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406523</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3939,6 +4084,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406532</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4053,6 +4203,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406541</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4167,6 +4322,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406550</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4281,6 +4441,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406558</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4395,6 +4560,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406573</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4509,6 +4679,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406597</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4623,6 +4798,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406604</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4737,6 +4917,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406611</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4851,6 +5036,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406627</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4965,6 +5155,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406649</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5079,6 +5274,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406669</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5193,6 +5393,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406673</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5307,6 +5512,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116473019</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5421,6 +5631,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406690</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5535,6 +5750,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406699</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5649,6 +5869,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406703</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5763,6 +5988,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406716</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5877,6 +6107,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406738</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5991,6 +6226,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406749</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6105,6 +6345,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406763</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6211,6 +6456,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116452742</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6325,6 +6575,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116473035</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6439,6 +6694,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116473071</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6553,6 +6813,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406529</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6667,8 +6932,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113406585</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>